--- a/data/信用债发行汇总_2026-07-17.xlsx
+++ b/data/信用债发行汇总_2026-07-17.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -699,6 +699,181 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07-17 18:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>26云能MTN004</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>102682656.IB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>云南省能源集团有限公司</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>云南省</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>24云能投GN001</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>4.93Y</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2.2567</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>中国银行股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>云南省能源集团有限公司2026年度第四期中期票据</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2031-07-20</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
